--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N56_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N56_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.33767272310851</v>
+        <v>8.342371817505134</v>
       </c>
       <c r="D2" t="n">
-        <v>51.13601570512495</v>
+        <v>8.309602552082806</v>
       </c>
       <c r="E2" t="n">
-        <v>8.990587790613748</v>
+        <v>1.460970515974734</v>
       </c>
       <c r="F2" t="n">
-        <v>17.29927556888114</v>
+        <v>2.811132279943185</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.35649714188101</v>
+        <v>5.420430785555665</v>
       </c>
       <c r="D3" t="n">
-        <v>85.73456684288723</v>
+        <v>13.93186711196918</v>
       </c>
       <c r="E3" t="n">
-        <v>8.990587790613748</v>
+        <v>1.460970515974734</v>
       </c>
       <c r="F3" t="n">
-        <v>17.29927556888114</v>
+        <v>2.811132279943185</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
